--- a/prac/2026/wetlands_BIO3018F_2026 complete.xlsx
+++ b/prac/2026/wetlands_BIO3018F_2026 complete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasper/GIT/BIO3018F/prac/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF94ED2-C3CD-D74D-ABA9-813391FE4BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EB20BB-06B3-EF4E-9D2F-EDB0FDD346E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="1360" windowWidth="26060" windowHeight="15560" xr2:uid="{DB49517A-0D61-2046-9DF1-E47353E179A4}"/>
+    <workbookView xWindow="30300" yWindow="-1520" windowWidth="25600" windowHeight="15500" xr2:uid="{DB49517A-0D61-2046-9DF1-E47353E179A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1101,7 +1101,7 @@
         <v>-34.403239999999997</v>
       </c>
       <c r="E12">
-        <v>20.56521</v>
+        <v>20.5655</v>
       </c>
       <c r="F12" t="s">
         <v>40</v>
@@ -1145,7 +1145,7 @@
         <v>-34.403239999999997</v>
       </c>
       <c r="E13">
-        <v>20.56521</v>
+        <v>20.5655</v>
       </c>
       <c r="F13" t="s">
         <v>40</v>
@@ -1189,7 +1189,7 @@
         <v>-34.403239999999997</v>
       </c>
       <c r="E14">
-        <v>20.56521</v>
+        <v>20.5655</v>
       </c>
       <c r="F14" t="s">
         <v>40</v>
@@ -1230,7 +1230,7 @@
         <v>-34.403239999999997</v>
       </c>
       <c r="E15">
-        <v>20.56521</v>
+        <v>20.5655</v>
       </c>
       <c r="F15" t="s">
         <v>40</v>
@@ -1271,7 +1271,7 @@
         <v>-34.403239999999997</v>
       </c>
       <c r="E16">
-        <v>20.56521</v>
+        <v>20.5655</v>
       </c>
       <c r="F16" t="s">
         <v>40</v>
@@ -1310,10 +1310,10 @@
         <v>26</v>
       </c>
       <c r="D17">
-        <v>-27.28763</v>
+        <v>-34.403851000000003</v>
       </c>
       <c r="E17">
-        <v>22.485510000000001</v>
+        <v>20.565113</v>
       </c>
       <c r="F17" t="s">
         <v>40</v>
@@ -1351,10 +1351,10 @@
         <v>26</v>
       </c>
       <c r="D18">
-        <v>-27.28763</v>
+        <v>-34.403851000000003</v>
       </c>
       <c r="E18">
-        <v>22.485510000000001</v>
+        <v>20.565113</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
@@ -1395,10 +1395,10 @@
         <v>26</v>
       </c>
       <c r="D19">
-        <v>-27.28763</v>
+        <v>-34.403851000000003</v>
       </c>
       <c r="E19">
-        <v>22.485510000000001</v>
+        <v>20.565113</v>
       </c>
       <c r="F19" t="s">
         <v>40</v>
@@ -1436,10 +1436,10 @@
         <v>26</v>
       </c>
       <c r="D20">
-        <v>-27.28763</v>
+        <v>-34.403851000000003</v>
       </c>
       <c r="E20">
-        <v>22.485510000000001</v>
+        <v>20.565113</v>
       </c>
       <c r="F20" t="s">
         <v>40</v>
@@ -1477,10 +1477,10 @@
         <v>26</v>
       </c>
       <c r="D21">
-        <v>-27.28763</v>
+        <v>-34.403851000000003</v>
       </c>
       <c r="E21">
-        <v>22.485510000000001</v>
+        <v>20.565113</v>
       </c>
       <c r="F21" t="s">
         <v>40</v>
@@ -1943,7 +1943,7 @@
         <v>-34.403149999999997</v>
       </c>
       <c r="E32">
-        <v>20.564810000000001</v>
+        <v>20.565000000000001</v>
       </c>
       <c r="F32" t="s">
         <v>40</v>
@@ -1987,7 +1987,7 @@
         <v>-34.403149999999997</v>
       </c>
       <c r="E33">
-        <v>20.564810000000001</v>
+        <v>20.565000000000001</v>
       </c>
       <c r="F33" t="s">
         <v>40</v>
@@ -2031,7 +2031,7 @@
         <v>-34.403149999999997</v>
       </c>
       <c r="E34">
-        <v>20.564810000000001</v>
+        <v>20.565000000000001</v>
       </c>
       <c r="F34" t="s">
         <v>40</v>
@@ -2072,7 +2072,7 @@
         <v>-34.403149999999997</v>
       </c>
       <c r="E35">
-        <v>20.564810000000001</v>
+        <v>20.565000000000001</v>
       </c>
       <c r="F35" t="s">
         <v>40</v>
@@ -2116,7 +2116,7 @@
         <v>-34.403149999999997</v>
       </c>
       <c r="E36">
-        <v>20.564810000000001</v>
+        <v>20.565000000000001</v>
       </c>
       <c r="F36" t="s">
         <v>40</v>
@@ -2361,10 +2361,10 @@
         <v>25</v>
       </c>
       <c r="D42">
-        <v>-34.403149999999997</v>
+        <v>-34.412452999999999</v>
       </c>
       <c r="E42">
-        <v>20.564810000000001</v>
+        <v>20.579114000000001</v>
       </c>
       <c r="F42" t="s">
         <v>40</v>
@@ -2405,10 +2405,10 @@
         <v>25</v>
       </c>
       <c r="D43">
-        <v>-34.403149999999997</v>
+        <v>-34.412452999999999</v>
       </c>
       <c r="E43">
-        <v>20.564810000000001</v>
+        <v>20.579114000000001</v>
       </c>
       <c r="F43" t="s">
         <v>40</v>
@@ -2446,10 +2446,10 @@
         <v>25</v>
       </c>
       <c r="D44">
-        <v>-34.403149999999997</v>
+        <v>-34.412452999999999</v>
       </c>
       <c r="E44">
-        <v>20.564810000000001</v>
+        <v>20.579114000000001</v>
       </c>
       <c r="F44" t="s">
         <v>40</v>
@@ -2490,10 +2490,10 @@
         <v>25</v>
       </c>
       <c r="D45">
-        <v>-34.403149999999997</v>
+        <v>-34.412452999999999</v>
       </c>
       <c r="E45">
-        <v>20.564810000000001</v>
+        <v>20.579114000000001</v>
       </c>
       <c r="F45" t="s">
         <v>40</v>
@@ -2534,10 +2534,10 @@
         <v>25</v>
       </c>
       <c r="D46">
-        <v>-34.403149999999997</v>
+        <v>-34.412452999999999</v>
       </c>
       <c r="E46">
-        <v>20.564810000000001</v>
+        <v>20.579114000000001</v>
       </c>
       <c r="F46" t="s">
         <v>40</v>
